--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_29-04-2026.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£15.28</t>
+          <t>£17.57</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>£14.99</t>
+          <t>£15.16</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£15.01</t>
+          <t>£17.26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>£17.58</t>
+          <t>£17.71</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£18.46</t>
+          <t>£21.23</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>£21.66</t>
+          <t>£22.59</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>£23.04</t>
+          <t>£23.48</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>£32.00</t>
+          <t>£33.04</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>£39.85</t>
+          <t>£40.42</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>£38.79</t>
+          <t>£39.80</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>£47.49</t>
+          <t>£48.87</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>£47.66</t>
+          <t>£49.45</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>£57.33</t>
+          <t>£59.76</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>£58.71</t>
+          <t>£60.39</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>£1216.67 Pre Sale Price-£1,250.00</t>
+          <t>£1308.33</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>£36.86</t>
+          <t>£42.39</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>£44.79</t>
+          <t>£51.50</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>£48.26</t>
+          <t>£52.34</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>£54.85</t>
+          <t>£62.31</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>£60.18</t>
+          <t>£69.20</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>£59.24</t>
+          <t>£68.11</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£57.15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>£57.08</t>
+          <t>£65.64</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>£1579.04</t>
+          <t>£1815.84</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>£1824.16</t>
+          <t>£2097.60</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>£1790.88</t>
+          <t>£2059.20</t>
         </is>
       </c>
     </row>
